--- a/file_upload_forms/037_image_upload_for_visual_effects--file_upload_forms.xlsx
+++ b/file_upload_forms/037_image_upload_for_visual_effects--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project Brief</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Project Description</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Brief description of the project</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,7 +555,11 @@
           <t>Reference Image</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>URL or upload reference image</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,7 +574,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>deadline</t>
+          <t>deadline_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,7 +582,11 @@
           <t>Deadline</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Date by which project needs to be completed</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>image_files</t>
+          <t>deadline_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Image Files</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Deadline Time</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Time by which project needs to be completed</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_brief_file</t>
+          <t>image_files</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Project Brief File</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Image Files</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select multiple image files</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>reference_image_file</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reference Image File</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Provide contact information</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>contact_info_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Email address</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>deadline_time</t>
+          <t>contact_info_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Contact Phone</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>contact_info_website</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Contact Website</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Website URL</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_brief_text</t>
+          <t>contact_info_address</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Project Brief</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Contact Address</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Street address</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_info_email</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Any additional notes or information</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>image_files_2</t>
+          <t>project_brief_file</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Image Files 2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Project Brief File</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Upload project brief file</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>image_files_3</t>
+          <t>project_brief_text</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Image Files 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Project Brief</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Brief description of the project</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_info_phone</t>
+          <t>image_files_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Image Files 2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select multiple image files</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deadline_date</t>
+          <t>image_files_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Image Files 3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select multiple image files</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>image_files_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Image Files 4</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Select multiple image files</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_info_website</t>
+          <t>image_files_5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Image Files 5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select multiple image files</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,20 +974,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>image_files_4</t>
+          <t>project_brief_file_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Image Files 4</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Project Brief File 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Upload project brief file 2</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -934,154 +1006,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_info_address</t>
+          <t>project_brief_text_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Project Brief 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Brief description of the project 2</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>deadline_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Deadline</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>contact_info_phone_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_brief_file_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Project Brief File</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>contact_info_phone_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>project_brief_text_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Project Brief</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>image_files_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Image Files 5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +1040,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1131,12 +1069,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1086,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1103,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1120,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1137,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1154,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1171,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1188,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1205,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1222,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1239,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1256,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1273,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1290,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1307,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
